--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_tarapaca.xlsx
@@ -404,7 +404,7 @@
         <v>27.25523196253476</v>
       </c>
       <c r="D2">
-        <v>1.807982854194504</v>
+        <v>3.564423578508086</v>
       </c>
       <c r="E2">
         <v>18.06385955985244</v>
@@ -429,7 +429,7 @@
         <v>35.64266081458386</v>
       </c>
       <c r="D3">
-        <v>1.930637414266837</v>
+        <v>6.190530634205394</v>
       </c>
       <c r="E3">
         <v>10.64169362457416</v>
@@ -454,7 +454,7 @@
         <v>33.77308707124011</v>
       </c>
       <c r="D4">
-        <v>1.716631280962491</v>
+        <v>4.08487706298417</v>
       </c>
       <c r="E4">
         <v>15.46918147241182</v>
@@ -479,7 +479,7 @@
         <v>49.35064935064935</v>
       </c>
       <c r="D5">
-        <v>1.079439252336449</v>
+        <v>2.31</v>
       </c>
       <c r="E5">
         <v>22.47191011235955</v>
@@ -504,7 +504,7 @@
         <v>21.98581560283688</v>
       </c>
       <c r="D6">
-        <v>2.243181818181818</v>
+        <v>4.426008968609866</v>
       </c>
       <c r="E6">
         <v>15.62718990889979</v>
@@ -529,7 +529,7 @@
         <v>49.42178940961656</v>
       </c>
       <c r="D7">
-        <v>1.177777777777778</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="E7">
         <v>19.19025674786043</v>
@@ -554,7 +554,7 @@
         <v>39.09404234367307</v>
       </c>
       <c r="D8">
-        <v>1.338826631509558</v>
+        <v>2.809128630705394</v>
       </c>
       <c r="E8">
         <v>20.37767756482525</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.25523196253476</v>
+      </c>
+      <c r="C2">
         <v>28.05502707449144</v>
-      </c>
-      <c r="C2">
-        <v>27.25523196253476</v>
       </c>
       <c r="D2">
         <v>3.564423578508086</v>
       </c>
       <c r="E2">
-        <v>18.06385955985244</v>
+        <v>17.54889350615085</v>
       </c>
       <c r="F2">
         <v>64.38724693399671</v>
       </c>
       <c r="G2">
-        <v>17.54889350615085</v>
+        <v>18.06385955985244</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>35.64266081458386</v>
+      </c>
+      <c r="C3">
         <v>16.15370408595609</v>
-      </c>
-      <c r="C3">
-        <v>35.64266081458386</v>
       </c>
       <c r="D3">
         <v>6.190530634205394</v>
       </c>
       <c r="E3">
-        <v>10.64169362457416</v>
+        <v>23.48057599267127</v>
       </c>
       <c r="F3">
         <v>65.87773038275458</v>
       </c>
       <c r="G3">
-        <v>23.48057599267127</v>
+        <v>10.64169362457416</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>33.77308707124011</v>
+      </c>
+      <c r="C4">
         <v>24.48054089709763</v>
-      </c>
-      <c r="C4">
-        <v>33.77308707124011</v>
       </c>
       <c r="D4">
         <v>4.08487706298417</v>
       </c>
       <c r="E4">
-        <v>15.46918147241182</v>
+        <v>21.34111394779347</v>
       </c>
       <c r="F4">
         <v>63.18970457979472</v>
       </c>
       <c r="G4">
-        <v>21.34111394779347</v>
+        <v>15.46918147241182</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>49.35064935064935</v>
+      </c>
+      <c r="C5">
         <v>43.29004329004329</v>
-      </c>
-      <c r="C5">
-        <v>49.35064935064935</v>
       </c>
       <c r="D5">
         <v>2.31</v>
       </c>
       <c r="E5">
-        <v>22.47191011235955</v>
+        <v>25.61797752808988</v>
       </c>
       <c r="F5">
         <v>51.91011235955057</v>
       </c>
       <c r="G5">
-        <v>25.61797752808988</v>
+        <v>22.47191011235955</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>21.98581560283688</v>
+      </c>
+      <c r="C6">
         <v>22.59371833839919</v>
-      </c>
-      <c r="C6">
-        <v>21.98581560283688</v>
       </c>
       <c r="D6">
         <v>4.426008968609866</v>
       </c>
       <c r="E6">
-        <v>15.62718990889979</v>
+        <v>15.20672740014015</v>
       </c>
       <c r="F6">
         <v>69.16608269096005</v>
       </c>
       <c r="G6">
-        <v>15.20672740014015</v>
+        <v>15.62718990889979</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>49.42178940961656</v>
+      </c>
+      <c r="C7">
         <v>35.48387096774194</v>
-      </c>
-      <c r="C7">
-        <v>49.42178940961656</v>
       </c>
       <c r="D7">
         <v>2.818181818181818</v>
       </c>
       <c r="E7">
-        <v>19.19025674786043</v>
+        <v>26.72811059907834</v>
       </c>
       <c r="F7">
         <v>54.08163265306122</v>
       </c>
       <c r="G7">
-        <v>26.72811059907834</v>
+        <v>19.19025674786043</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>39.09404234367307</v>
+      </c>
+      <c r="C8">
         <v>35.59822747415066</v>
-      </c>
-      <c r="C8">
-        <v>39.09404234367307</v>
       </c>
       <c r="D8">
         <v>2.809128630705394</v>
       </c>
       <c r="E8">
-        <v>20.37767756482525</v>
+        <v>22.37880496054115</v>
       </c>
       <c r="F8">
         <v>57.2435174746336</v>
       </c>
       <c r="G8">
-        <v>22.37880496054115</v>
+        <v>20.37767756482525</v>
       </c>
     </row>
   </sheetData>
